--- a/SocialMedia.xlsx
+++ b/SocialMedia.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/quicksoftwares_global?igsh=MTI2dDcyb3kweDZ1NA==</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/SocialMedia.xlsx
+++ b/SocialMedia.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SocialMedia" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContactEmail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,4 +492,35 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>quicksoftwares.global@gmail.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SocialMedia.xlsx
+++ b/SocialMedia.xlsx
@@ -1,41 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7731AC5C-2071-3646-A72F-6EEEBCDF4640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SocialMedia" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContactEmail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SocialMedia" sheetId="1" r:id="rId1"/>
+    <sheet name="ContactEmail" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>https://youtube.com/@quicksoftwares-prt?feature=shared</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/quicksoftwares_global?igsh=MTI2dDcyb3kweDZ1NA==</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>contact@quicksoftwares.net</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,85 +122,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,84 +450,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+    <col min="3" max="3" width="72.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Whatsapp</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Youtube</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://wa.me/917838127423</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@quicksoftwares-prt?feature=shared</t>
-        </is>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://wa.me/16472614931</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/quicksoftwares_global?igsh=MTI2dDcyb3kweDZ1NA==</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@quicksoftwares-prt?feature=shared</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -495,32 +509,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
+    <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>quicksoftwares.global@gmail.com</t>
-        </is>
+    <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{29EEDAEB-0380-474D-93DD-CC19C8501113}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SocialMedia.xlsx
+++ b/SocialMedia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7731AC5C-2071-3646-A72F-6EEEBCDF4640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAAB49D-4945-5A44-A366-4B473506BBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Currency</t>
   </si>
@@ -41,9 +41,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>https://youtube.com/@quicksoftwares-prt?feature=shared</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -54,6 +51,9 @@
   </si>
   <si>
     <t>contact@quicksoftwares.net</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@QuickSoftwares-Global</t>
   </si>
 </sst>
 </file>
@@ -142,12 +142,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -479,31 +480,35 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
+      <c r="B2" s="3">
+        <v>917838127423</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{21BB09A5-692A-804A-840C-3293758D49F3}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{2D313071-A99D-AE44-9CD2-7B63E13B8DB3}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -518,12 +523,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/SocialMedia.xlsx
+++ b/SocialMedia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAAB49D-4945-5A44-A366-4B473506BBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4F8259-ABD0-BC41-B16B-4721EB77B3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Currency</t>
   </si>
@@ -60,9 +60,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,15 +147,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -456,7 +467,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="9" customWidth="1"/>
     <col min="3" max="3" width="72.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.83203125" style="1"/>
@@ -466,7 +477,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -480,8 +491,8 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <v>917838127423</v>
+      <c r="B2" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
@@ -494,7 +505,7 @@
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
